--- a/investors/VYTALIX_INVESTOR_CRM.xlsx
+++ b/investors/VYTALIX_INVESTOR_CRM.xlsx
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
